--- a/assets/constructions/examples/ctd_arbm_drillingchuck.xlsx
+++ b/assets/constructions/examples/ctd_arbm_drillingchuck.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="ctd" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="ctd" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AG6"/>
+  <dimension ref="A1:AK6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -594,51 +594,77 @@
           <t>adintws</t>
         </is>
       </c>
+      <c r="AH1" s="1" t="inlineStr">
+        <is>
+          <t>lcs</t>
+        </is>
+      </c>
+      <c r="AI1" s="1" t="inlineStr">
+        <is>
+          <t>pricevalue</t>
+        </is>
+      </c>
+      <c r="AJ1" s="1" t="inlineStr">
+        <is>
+          <t>pricecurrency</t>
+        </is>
+      </c>
+      <c r="AK1" s="1" t="inlineStr">
+        <is>
+          <t>pricevalue_rub</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>SK40-SPU13-110</t>
+          <t>NT30-APU08-80</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>DEREK</t>
+          <t>AMATI</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Сверлильные патроны SK-SPU</t>
+          <t>Патрон сверлильный NT-APU</t>
         </is>
       </c>
       <c r="D2" t="inlineStr"/>
       <c r="E2" t="n">
-        <v>110</v>
-      </c>
-      <c r="F2" t="inlineStr"/>
+        <v>80</v>
+      </c>
+      <c r="F2" t="n">
+        <v>80</v>
+      </c>
       <c r="G2" t="inlineStr"/>
       <c r="H2" t="n">
-        <v>50</v>
+        <v>38</v>
       </c>
       <c r="I2" t="inlineStr"/>
       <c r="J2" t="inlineStr"/>
       <c r="K2" t="inlineStr"/>
-      <c r="L2" t="inlineStr"/>
+      <c r="L2" t="n">
+        <v>90</v>
+      </c>
       <c r="M2" t="inlineStr"/>
       <c r="N2" t="n">
-        <v>63.55</v>
+        <v>50</v>
       </c>
       <c r="O2" t="inlineStr">
         <is>
-          <t>HA-0.3..13</t>
+          <t>HA-1..8</t>
         </is>
       </c>
       <c r="P2" t="inlineStr"/>
       <c r="Q2" t="inlineStr"/>
       <c r="R2" t="inlineStr"/>
-      <c r="S2" t="inlineStr"/>
+      <c r="S2" t="n">
+        <v>1</v>
+      </c>
       <c r="T2" t="n">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="U2" t="inlineStr"/>
       <c r="V2" t="inlineStr"/>
@@ -652,48 +678,68 @@
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>DIN_69871:SK40</t>
+          <t>DIN_2080:NT30</t>
         </is>
       </c>
       <c r="AB2" t="inlineStr"/>
-      <c r="AC2" t="inlineStr"/>
-      <c r="AD2" t="n">
-        <v>1.76</v>
-      </c>
+      <c r="AC2" t="inlineStr">
+        <is>
+          <t>DIN 2080</t>
+        </is>
+      </c>
+      <c r="AD2" t="inlineStr"/>
       <c r="AE2" t="n">
         <v>0</v>
       </c>
       <c r="AF2" t="inlineStr">
         <is>
-          <t>2019/DEREK Металлорежущий инструмент и оснастка</t>
+          <t>2025 / AMATI Инструментальная и технологическая оснастка</t>
         </is>
       </c>
       <c r="AG2" t="inlineStr">
         <is>
-          <t>HA-0.3..13</t>
-        </is>
+          <t>HA-1..8</t>
+        </is>
+      </c>
+      <c r="AH2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AI2" t="n">
+        <v>504</v>
+      </c>
+      <c r="AJ2" t="inlineStr">
+        <is>
+          <t>CNY</t>
+        </is>
+      </c>
+      <c r="AK2" t="n">
+        <v>6189.42</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>SK40-APU16-125</t>
+          <t>BT30-SPU16-120</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>LIKON</t>
-        </is>
-      </c>
-      <c r="C3" t="inlineStr"/>
+          <t>DEREK</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>Сверлильные патроны BT-SPU</t>
+        </is>
+      </c>
       <c r="D3" t="inlineStr"/>
       <c r="E3" t="n">
-        <v>127</v>
+        <v>120</v>
       </c>
       <c r="F3" t="inlineStr"/>
       <c r="G3" t="inlineStr"/>
       <c r="H3" t="n">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="I3" t="inlineStr"/>
       <c r="J3" t="inlineStr"/>
@@ -701,7 +747,7 @@
       <c r="L3" t="inlineStr"/>
       <c r="M3" t="inlineStr"/>
       <c r="N3" t="n">
-        <v>63.55</v>
+        <v>46</v>
       </c>
       <c r="O3" t="inlineStr">
         <is>
@@ -729,46 +775,66 @@
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>DIN_69871:SK40</t>
+          <t>JIS_B_6339_MAS_403:BT30</t>
         </is>
       </c>
       <c r="AB3" t="inlineStr"/>
       <c r="AC3" t="inlineStr"/>
-      <c r="AD3" t="inlineStr"/>
+      <c r="AD3" t="n">
+        <v>1.7</v>
+      </c>
       <c r="AE3" t="n">
         <v>0</v>
       </c>
       <c r="AF3" t="inlineStr">
         <is>
-          <t>2022/LIKON Инструментальный каталог</t>
+          <t>2019/DEREK Металлорежущий инструмент и оснастка</t>
         </is>
       </c>
       <c r="AG3" t="inlineStr">
         <is>
           <t>HA-3..16</t>
         </is>
+      </c>
+      <c r="AH3" t="n">
+        <v>1</v>
+      </c>
+      <c r="AI3" t="n">
+        <v>201.47</v>
+      </c>
+      <c r="AJ3" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="AK3" t="n">
+        <v>16515.28</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>SK50-APU08-90</t>
+          <t>BT30-SPU8-80</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>LIKON</t>
-        </is>
-      </c>
-      <c r="C4" t="inlineStr"/>
+          <t>DEREK</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>Сверлильные патроны BT-SPU</t>
+        </is>
+      </c>
       <c r="D4" t="inlineStr"/>
       <c r="E4" t="n">
-        <v>97.5</v>
+        <v>80</v>
       </c>
       <c r="F4" t="inlineStr"/>
       <c r="G4" t="inlineStr"/>
       <c r="H4" t="n">
-        <v>36.3</v>
+        <v>37</v>
       </c>
       <c r="I4" t="inlineStr"/>
       <c r="J4" t="inlineStr"/>
@@ -776,18 +842,18 @@
       <c r="L4" t="inlineStr"/>
       <c r="M4" t="inlineStr"/>
       <c r="N4" t="n">
-        <v>97.5</v>
+        <v>46</v>
       </c>
       <c r="O4" t="inlineStr">
         <is>
-          <t>HA-1..8</t>
+          <t>HA-0..8</t>
         </is>
       </c>
       <c r="P4" t="inlineStr"/>
       <c r="Q4" t="inlineStr"/>
       <c r="R4" t="inlineStr"/>
       <c r="S4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T4" t="n">
         <v>8</v>
@@ -804,68 +870,92 @@
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>DIN_69871:SK50</t>
+          <t>JIS_B_6339_MAS_403:BT30</t>
         </is>
       </c>
       <c r="AB4" t="inlineStr"/>
       <c r="AC4" t="inlineStr"/>
-      <c r="AD4" t="inlineStr"/>
+      <c r="AD4" t="n">
+        <v>0.72</v>
+      </c>
       <c r="AE4" t="n">
         <v>0</v>
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>2022/LIKON Инструментальный каталог</t>
+          <t>2019/DEREK Металлорежущий инструмент и оснастка</t>
         </is>
       </c>
       <c r="AG4" t="inlineStr">
         <is>
-          <t>HA-1..8</t>
-        </is>
+          <t>HA-0..8</t>
+        </is>
+      </c>
+      <c r="AH4" t="n">
+        <v>1</v>
+      </c>
+      <c r="AI4" t="n">
+        <v>201.47</v>
+      </c>
+      <c r="AJ4" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="AK4" t="n">
+        <v>16515.28</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>SK30-APU13-120</t>
+          <t>SK30-APU16-130</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>LIKON</t>
-        </is>
-      </c>
-      <c r="C5" t="inlineStr"/>
+          <t>AMATI</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>Патрон сверлильный SK-APU</t>
+        </is>
+      </c>
       <c r="D5" t="inlineStr"/>
       <c r="E5" t="n">
-        <v>124.5</v>
-      </c>
-      <c r="F5" t="inlineStr"/>
+        <v>130</v>
+      </c>
+      <c r="F5" t="n">
+        <v>130</v>
+      </c>
       <c r="G5" t="inlineStr"/>
       <c r="H5" t="n">
-        <v>51.5</v>
+        <v>53</v>
       </c>
       <c r="I5" t="inlineStr"/>
       <c r="J5" t="inlineStr"/>
       <c r="K5" t="inlineStr"/>
-      <c r="L5" t="inlineStr"/>
+      <c r="L5" t="n">
+        <v>140.6</v>
+      </c>
       <c r="M5" t="inlineStr"/>
       <c r="N5" t="n">
         <v>50</v>
       </c>
       <c r="O5" t="inlineStr">
         <is>
-          <t>HA-1..13</t>
+          <t>HA-3..16</t>
         </is>
       </c>
       <c r="P5" t="inlineStr"/>
       <c r="Q5" t="inlineStr"/>
       <c r="R5" t="inlineStr"/>
       <c r="S5" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="T5" t="n">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="U5" t="inlineStr"/>
       <c r="V5" t="inlineStr"/>
@@ -883,46 +973,60 @@
         </is>
       </c>
       <c r="AB5" t="inlineStr"/>
-      <c r="AC5" t="inlineStr"/>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>DIN 69871</t>
+        </is>
+      </c>
       <c r="AD5" t="inlineStr"/>
       <c r="AE5" t="n">
         <v>0</v>
       </c>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>2022/LIKON Инструментальный каталог</t>
+          <t>2025 / AMATI Инструментальная и технологическая оснастка</t>
         </is>
       </c>
       <c r="AG5" t="inlineStr">
         <is>
-          <t>HA-1..13</t>
-        </is>
+          <t>HA-3..16</t>
+        </is>
+      </c>
+      <c r="AH5" t="n">
+        <v>1</v>
+      </c>
+      <c r="AI5" t="n">
+        <v>952</v>
+      </c>
+      <c r="AJ5" t="inlineStr">
+        <is>
+          <t>CNY</t>
+        </is>
+      </c>
+      <c r="AK5" t="n">
+        <v>11691.13</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>SK50-SPU13-100</t>
+          <t>BT50-APU16-130</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>DEREK</t>
-        </is>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Сверлильные патроны SK-SPU</t>
-        </is>
-      </c>
+          <t>LIKON</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr"/>
       <c r="D6" t="inlineStr"/>
       <c r="E6" t="n">
-        <v>100</v>
+        <v>130</v>
       </c>
       <c r="F6" t="inlineStr"/>
       <c r="G6" t="inlineStr"/>
       <c r="H6" t="n">
-        <v>50</v>
+        <v>58</v>
       </c>
       <c r="I6" t="inlineStr"/>
       <c r="J6" t="inlineStr"/>
@@ -930,19 +1034,21 @@
       <c r="L6" t="inlineStr"/>
       <c r="M6" t="inlineStr"/>
       <c r="N6" t="n">
-        <v>97.5</v>
+        <v>100</v>
       </c>
       <c r="O6" t="inlineStr">
         <is>
-          <t>HA-0.3..13</t>
+          <t>HA-3..16</t>
         </is>
       </c>
       <c r="P6" t="inlineStr"/>
       <c r="Q6" t="inlineStr"/>
       <c r="R6" t="inlineStr"/>
-      <c r="S6" t="inlineStr"/>
+      <c r="S6" t="n">
+        <v>3</v>
+      </c>
       <c r="T6" t="n">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="U6" t="inlineStr"/>
       <c r="V6" t="inlineStr"/>
@@ -956,27 +1062,31 @@
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>DIN_69871:SK50</t>
+          <t>JIS_B_6339_MAS_403:BT50</t>
         </is>
       </c>
       <c r="AB6" t="inlineStr"/>
       <c r="AC6" t="inlineStr"/>
-      <c r="AD6" t="n">
-        <v>4.5</v>
-      </c>
+      <c r="AD6" t="inlineStr"/>
       <c r="AE6" t="n">
         <v>0</v>
       </c>
       <c r="AF6" t="inlineStr">
         <is>
-          <t>2019/DEREK Металлорежущий инструмент и оснастка</t>
+          <t>2022/LIKON Инструментальный каталог</t>
         </is>
       </c>
       <c r="AG6" t="inlineStr">
         <is>
-          <t>HA-0.3..13</t>
-        </is>
-      </c>
+          <t>HA-3..16</t>
+        </is>
+      </c>
+      <c r="AH6" t="n">
+        <v>1</v>
+      </c>
+      <c r="AI6" t="inlineStr"/>
+      <c r="AJ6" t="inlineStr"/>
+      <c r="AK6" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
